--- a/data/gravel/Whyte Verro 2025.xlsx
+++ b/data/gravel/Whyte Verro 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5410B59-3E06-0147-A847-C1469EB4545E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BB26CC-0EC0-0B42-A49C-B662817DC71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="18100" windowHeight="10280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://whytebikes.com/cdn/shop/files/VERRO-RES-SIDE_1680x.jpg?v=1751888783</t>
   </si>
 </sst>
 </file>
@@ -709,6 +712,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Whyte Verro 2025.xlsx
+++ b/data/gravel/Whyte Verro 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BB26CC-0EC0-0B42-A49C-B662817DC71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632344B6-516C-8047-8619-B2B846635283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="18100" windowHeight="10280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11420" yWindow="2360" windowWidth="19160" windowHeight="14800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -313,9 +313,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -335,17 +332,32 @@
   </si>
   <si>
     <t>https://whytebikes.com/cdn/shop/files/VERRO-RES-SIDE_1680x.jpg?v=1751888783</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>St Leonards-on-Sea, East Sussex, United Kingdom</t>
+  </si>
+  <si>
+    <t>GBP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -368,8 +380,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -666,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -714,7 +727,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1178,26 +1191,26 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
         <v>98</v>
-      </c>
-      <c r="B35" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" t="s">
         <v>100</v>
-      </c>
-      <c r="B36" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" t="s">
         <v>102</v>
-      </c>
-      <c r="B37" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1407,8 +1420,16 @@
       <c r="A72" t="s">
         <v>96</v>
       </c>
-      <c r="B72" t="s">
-        <v>97</v>
+      <c r="B72" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>104</v>
+      </c>
+      <c r="B73" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Whyte Verro 2025.xlsx
+++ b/data/gravel/Whyte Verro 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632344B6-516C-8047-8619-B2B846635283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F0A717-9A3C-6F4C-9762-24120165533A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11420" yWindow="2360" windowWidth="19160" windowHeight="14800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9640" yWindow="2360" windowWidth="19160" windowHeight="14800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>GBP</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1337,6 +1340,9 @@
       <c r="A59" t="s">
         <v>81</v>
       </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">

--- a/data/gravel/Whyte Verro 2025.xlsx
+++ b/data/gravel/Whyte Verro 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F0A717-9A3C-6F4C-9762-24120165533A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7948A7DB-3A77-9B44-AE60-207F1DB83EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9640" yWindow="2360" windowWidth="19160" windowHeight="14800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -344,6 +344,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -682,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1282,159 +1300,189 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>69</v>
-      </c>
-      <c r="B49" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>73</v>
-      </c>
-      <c r="B52" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>69</v>
+      </c>
+      <c r="B55" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>80</v>
+        <v>73</v>
+      </c>
+      <c r="B58" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>81</v>
-      </c>
-      <c r="B59" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>84</v>
-      </c>
-      <c r="B62" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>87</v>
-      </c>
-      <c r="B64" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>89</v>
-      </c>
-      <c r="B66" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="B71" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>96</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>106</v>
+        <v>89</v>
+      </c>
+      <c r="B72" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>96</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>104</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>105</v>
       </c>
     </row>
